--- a/pages/shp/uploads/24-06-2026 - 24-06-2026.xlsx
+++ b/pages/shp/uploads/24-06-2026 - 24-06-2026.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="328">
   <si>
     <t>NOMOR AJU</t>
   </si>
@@ -347,46 +347,85 @@
     <t>FLAG PROPORSIONAL NETTO</t>
   </si>
   <si>
-    <t>000261NIW34520260624000470</t>
-  </si>
-  <si>
-    <t>261</t>
+    <t>000030NIW34520260624001022</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>040300</t>
   </si>
   <si>
     <t>050500</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>IDTPP</t>
+  </si>
+  <si>
+    <t>USLAX</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
+    <t>DN</t>
+  </si>
+  <si>
     <t>BANDUNG</t>
   </si>
   <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
     <t>YUS YULIUS</t>
   </si>
   <si>
-    <t>EXIM MANAGER</t>
-  </si>
-  <si>
-    <t>IDR</t>
-  </si>
-  <si>
-    <t>014062</t>
-  </si>
-  <si>
-    <t>000261NIW34520260624000471</t>
-  </si>
-  <si>
-    <t>014067</t>
-  </si>
-  <si>
-    <t>000261NIW34520260624000469</t>
-  </si>
-  <si>
-    <t>014008</t>
+    <t>MANAGER EXIM</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>EXW</t>
+  </si>
+  <si>
+    <t>382239</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>000030NIW34520260624001023</t>
+  </si>
+  <si>
+    <t>382255</t>
+  </si>
+  <si>
+    <t>000030NIW34520260624001024</t>
+  </si>
+  <si>
+    <t>382281</t>
   </si>
   <si>
     <t>KODE FASILITAS TARIF</t>
@@ -401,87 +440,106 @@
     <t>NPWP BILLING</t>
   </si>
   <si>
+    <t>SERI</t>
+  </si>
+  <si>
+    <t>KODE ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS IDENTITAS</t>
+  </si>
+  <si>
+    <t>NOMOR IDENTITAS</t>
+  </si>
+  <si>
+    <t>NAMA ENTITAS</t>
+  </si>
+  <si>
+    <t>ALAMAT ENTITAS</t>
+  </si>
+  <si>
+    <t>NIB ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS API</t>
+  </si>
+  <si>
+    <t>KODE STATUS</t>
+  </si>
+  <si>
+    <t>NOMOR IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>TANGGAL IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE NEGARA</t>
+  </si>
+  <si>
+    <t>NIPER ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE KATEGORI KONSOLIDATOR</t>
+  </si>
+  <si>
+    <t>KODE AFILIASI</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>0926856451045000000000</t>
+  </si>
+  <si>
+    <t>KBN PRIMA LOGISTIK</t>
+  </si>
+  <si>
+    <t>GEDUNG MAWAR, JALAN RAYA CAKUNG CILINCING, TANJUNG PRIOK  RT.000 RW.000, SUKAPURA, CILINCING, KOTA ADMINISTRASI JAKARTA UTARA, DAERAH KHUSUS IBUKOTA JAKARTA</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>LAINNYA</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>BM</t>
-  </si>
-  <si>
-    <t>PPN</t>
-  </si>
-  <si>
-    <t>BMTP</t>
-  </si>
-  <si>
-    <t>PPH</t>
-  </si>
-  <si>
-    <t>SERI</t>
-  </si>
-  <si>
-    <t>KODE ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS IDENTITAS</t>
-  </si>
-  <si>
-    <t>NOMOR IDENTITAS</t>
-  </si>
-  <si>
-    <t>NAMA ENTITAS</t>
-  </si>
-  <si>
-    <t>ALAMAT ENTITAS</t>
-  </si>
-  <si>
-    <t>NIB ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS API</t>
-  </si>
-  <si>
-    <t>KODE STATUS</t>
-  </si>
-  <si>
-    <t>NOMOR IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>TANGGAL IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE NEGARA</t>
-  </si>
-  <si>
-    <t>NIPER ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE KATEGORI KONSOLIDATOR</t>
-  </si>
-  <si>
-    <t>KODE AFILIASI</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>0025445305441000000000</t>
-  </si>
-  <si>
-    <t>GUNAJAYA SANTOSA</t>
-  </si>
-  <si>
-    <t>JALAN RANCAJIGANG NO.110 RT.004 RW.010, PADAMULYA, MAJALAYA, KABUPATEN BANDUNG, JAWA BARAT</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>LAINNYA</t>
+    <t>WESTERN OMNI WEO-0008</t>
+  </si>
+  <si>
+    <t>3400 NORTH GAP DR
+FRESNO, CA
+93727</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>000000000000000</t>
+  </si>
+  <si>
+    <t>KANMAX ENTERPRISES LTD</t>
+  </si>
+  <si>
+    <t>60 PAYA LEBAR ROAD #04-21 PAYA LEBAR SQUARE 409051 SINGAPORE</t>
+  </si>
+  <si>
+    <t>OLD NAVY, LLC</t>
+  </si>
+  <si>
+    <t>2 FOLSOM STREET
+SAN FRANCISCO, CALIFORNIA
+94105</t>
+  </si>
+  <si>
     <t>0745406926444000000000</t>
   </si>
   <si>
@@ -491,157 +549,58 @@
     <t>JL RAYA RANCAEKEK MAJALAYA NO.289 RT.002 RW.007, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
   </si>
   <si>
+    <t>0220103231143</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>JALAN RAYA RANCAEKAEK MAJALAYA NO.289 001/007</t>
-  </si>
-  <si>
-    <t>0220103231143</t>
+    <t>NOMOR DOKUMEN</t>
+  </si>
+  <si>
+    <t>TANGGAL DOKUMEN</t>
+  </si>
+  <si>
+    <t>KODE FASILITAS</t>
+  </si>
+  <si>
+    <t>KODE IJIN</t>
+  </si>
+  <si>
+    <t>920</t>
   </si>
   <si>
     <t>16/MK/WBC.09/2026</t>
   </si>
   <si>
-    <t>01-20-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>0739377943422000000000</t>
-  </si>
-  <si>
-    <t>HARMONY TUNAS PRIMA</t>
-  </si>
-  <si>
-    <t>JALAN CIRANGRANG BARAT NO.02 RT.002 RW.001, MARGAHAYU UTARA, BABAKAN CIPARAY, KOTA BANDUNG, JAWA BARAT</t>
-  </si>
-  <si>
-    <t>NOMOR DOKUMEN</t>
-  </si>
-  <si>
-    <t>TANGGAL DOKUMEN</t>
-  </si>
-  <si>
-    <t>KODE FASILITAS</t>
-  </si>
-  <si>
-    <t>KODE IJIN</t>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>0347ENAG0626</t>
   </si>
   <si>
     <t>217</t>
   </si>
   <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>GG/OUT/0626/00105,GG/OUT/0626/00106</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>018302</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>015248</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>2344/TPB-SK.01/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>173/NAG/KK/VI/2026</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>997</t>
-  </si>
-  <si>
-    <t>CBD 2026 06 898 01 15913</t>
-  </si>
-  <si>
-    <t>994</t>
-  </si>
-  <si>
-    <t>001995/BPJ/CB/2026</t>
-  </si>
-  <si>
-    <t>2314/TPB-SK.01/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>170/NAG/KK/V/2026</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>CBD 2026 06 898 01 15711</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>001973/BPJ/CB/2026</t>
-  </si>
-  <si>
-    <t>005</t>
-  </si>
-  <si>
-    <t>GG/OUT/0626/00107,GG/OUT/0626/00108,GG/OUT/0626/00109,GG/OUT/0626/00110</t>
-  </si>
-  <si>
-    <t>020931</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>019632</t>
-  </si>
-  <si>
-    <t>2026-05-20</t>
-  </si>
-  <si>
-    <t>2267/TPB-SK.01/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>161/NAG/KK/V/2026</t>
-  </si>
-  <si>
-    <t>CBD 2026 06 898 01 15460</t>
-  </si>
-  <si>
-    <t>001926/BPJ/CB/2026</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>014360</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
+    <t>014766</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>015026</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>0348ENAG0626</t>
+  </si>
+  <si>
+    <t>0349ENAG0626</t>
   </si>
   <si>
     <t>KODE CARA ANGKUT</t>
@@ -665,6 +624,15 @@
     <t>CARA PENGANGKUTAN LAINNYA</t>
   </si>
   <si>
+    <t>JOSEPHINE MAERSK</t>
+  </si>
+  <si>
+    <t>VV 626N</t>
+  </si>
+  <si>
+    <t>DK</t>
+  </si>
+  <si>
     <t>KODE KEMASAN</t>
   </si>
   <si>
@@ -677,10 +645,10 @@
     <t>NOMOR SEGEL</t>
   </si>
   <si>
-    <t>RO</t>
-  </si>
-  <si>
-    <t>PK</t>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>OLD NAVY</t>
   </si>
   <si>
     <t>NOMOR KONTINER</t>
@@ -854,49 +822,37 @@
     <t>STATEMENT PERBEDAAN HARGA</t>
   </si>
   <si>
-    <t>54071099</t>
-  </si>
-  <si>
-    <t>KN_1</t>
-  </si>
-  <si>
-    <t>FABRIC UNTUK DI CELUP ( SINGLE JERSEY 54% COTTON 36% MODAL 10% SPANDEX )</t>
+    <t>61102000</t>
+  </si>
+  <si>
+    <t>KNM/0526/285</t>
+  </si>
+  <si>
+    <t>TANKTOP
+PO : 61779304 STYLE: 692926 WOMENS COTTON FIBERS, KNIT PULLOVER 95% COTTON 5% ELASTANE, COLOR : BLACK COFFEE, BLACK JACK 3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>KGM</t>
+    <t>PCE</t>
+  </si>
+  <si>
+    <t>3204</t>
   </si>
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>54078200</t>
-  </si>
-  <si>
-    <t>KN_2</t>
-  </si>
-  <si>
-    <t>FABRIC UNTUK DI CELUP ( FABRIC 90% MODAL 10% SPANDEX SINGLE JERSEY )</t>
-  </si>
-  <si>
-    <t>62101019</t>
-  </si>
-  <si>
-    <t>2910</t>
-  </si>
-  <si>
-    <t>PANEL UNTUK DI PRINTING ( KNITTED FABRIC 30S/1 CVC JERSEY KNITTED FABRIC ( 60% BCI COTTON 40% POLYESTER )</t>
-  </si>
-  <si>
-    <t>PCE</t>
-  </si>
-  <si>
-    <t>HK</t>
+    <t>KNM/0526/281</t>
+  </si>
+  <si>
+    <t>TANKTOP
+PO : 62023521 STYLE: 692926 WOMENS COTTON FIBERS, KNIT PULLOVER 95% COTTON 5% ELASTANE, COLOR : BLUSH ON YOU</t>
+  </si>
+  <si>
+    <t>TANKTOP
+PO : 62023525 STYLE: 692926 WOMENS COTTON FIBERS, KNIT PULLOVER 95% COTTON 5% ELASTANE, COLOR : SHOOTING STAR</t>
   </si>
   <si>
     <t>KODE PUNGUTAN</t>
@@ -956,75 +912,6 @@
     <t>VALUTA</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>54024490</t>
-  </si>
-  <si>
-    <t>YRN_6</t>
-  </si>
-  <si>
-    <t>SPANDEX BARE YARN 40D H-550, BR, LOT:Z4700</t>
-  </si>
-  <si>
-    <t>04-21-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>000023NIW34520260421000124</t>
-  </si>
-  <si>
-    <t>52062400</t>
-  </si>
-  <si>
-    <t>NE 40/1 LENZING MODAL/MARTIN COTTON 4060 COMBED HOSIERY COMPACT YARN</t>
-  </si>
-  <si>
-    <t>05-12-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>000023NIW34520260512000142</t>
-  </si>
-  <si>
-    <t>SPANDEX BARE YARN R/W 30D H-350 BRT ON CHEESE - Z3229</t>
-  </si>
-  <si>
-    <t>05-20-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>000023NIW34520260520000148</t>
-  </si>
-  <si>
-    <t>55101100</t>
-  </si>
-  <si>
-    <t>BIRLA MICROMODAL FSC YARN FOR KNITTING WAXED ON PAPER NEUTRAL CONES NE50/1 COMPACT SIRO</t>
-  </si>
-  <si>
-    <t>05-28-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>000023NIW34520260528000160</t>
-  </si>
-  <si>
-    <t>60062200</t>
-  </si>
-  <si>
-    <t>KNITTED FABRIC 30S/1 CVC JERSEY KNITTED FABRIC (60% BCI COTTON 40% POLYESTER) (28129 YRD)</t>
-  </si>
-  <si>
-    <t>SPROUTS GREEN 2259C</t>
-  </si>
-  <si>
-    <t>04-16-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>000023NIW34520260416000108</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>KODE_ASAL_BAHAN_BAKU</t>
   </si>
   <si>
@@ -1052,30 +939,15 @@
     <t>TANGGAL BPJ</t>
   </si>
   <si>
-    <t>06-09-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>JAMKRIDA JAKARTA</t>
-  </si>
-  <si>
-    <t>09-07-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>06-08-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>09-03-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>06-03-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>08-31-2026 00:00:00</t>
-  </si>
-  <si>
     <t>NAMA</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>BANK BCA</t>
+  </si>
+  <si>
     <t>JENIS NILAI</t>
   </si>
   <si>
@@ -1142,16 +1014,16 @@
     <t>TANGGAL RESPON</t>
   </si>
   <si>
-    <t>26108</t>
-  </si>
-  <si>
-    <t>014231/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>014236/KBC.0903/2026</t>
-  </si>
-  <si>
-    <t>014177/KBC.0903/2026</t>
+    <t>3015</t>
+  </si>
+  <si>
+    <t>382211/PM/KPU.1/2026</t>
+  </si>
+  <si>
+    <t>382195/PM/KPU.1/2026</t>
+  </si>
+  <si>
+    <t>382237/PM/KPU.1/2026</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1151,6 @@
     <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="73" max="73" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1645,15 +1516,66 @@
       <c r="C2" t="s">
         <v>106</v>
       </c>
-      <c r="N2" t="s">
+      <c r="E2" t="s">
         <v>107</v>
       </c>
+      <c r="G2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P2" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>110</v>
+      </c>
+      <c r="W2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>119</v>
+      </c>
       <c r="BK2" t="n">
         <v>0.0</v>
       </c>
       <c r="BL2" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN2" t="n">
+        <v>1999.56</v>
+      </c>
       <c r="BO2" t="n">
         <v>0.0</v>
       </c>
@@ -1661,7 +1583,7 @@
         <v>0.0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0</v>
+        <v>6445.95</v>
       </c>
       <c r="BR2" t="n">
         <v>0.0</v>
@@ -1673,13 +1595,13 @@
         <v>0.0</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.1737403264E8</v>
+        <v>0.0</v>
       </c>
       <c r="BV2" t="n">
         <v>0.0</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.0</v>
+        <v>17781.0</v>
       </c>
       <c r="BY2" t="n">
         <v>0.0</v>
@@ -1688,42 +1610,54 @@
         <v>0.0</v>
       </c>
       <c r="CB2" t="n">
-        <v>1244.05</v>
+        <v>346.12</v>
       </c>
       <c r="CC2" t="n">
-        <v>1244.05</v>
+        <v>308.72</v>
       </c>
       <c r="CD2" t="n">
         <v>0.0</v>
       </c>
       <c r="CE2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>117</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>121</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>124</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>125</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>117</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>126</v>
+      </c>
+      <c r="DB2" t="s">
         <v>108</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>109</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>112</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>113</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>109</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s">
         <v>105</v>
@@ -1731,15 +1665,66 @@
       <c r="C3" t="s">
         <v>106</v>
       </c>
-      <c r="N3" t="s">
+      <c r="E3" t="s">
         <v>107</v>
       </c>
+      <c r="G3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" t="s">
+        <v>108</v>
+      </c>
+      <c r="P3" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>119</v>
+      </c>
       <c r="BK3" t="n">
         <v>0.0</v>
       </c>
       <c r="BL3" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN3" t="n">
+        <v>684.76</v>
+      </c>
       <c r="BO3" t="n">
         <v>0.0</v>
       </c>
@@ -1747,7 +1732,7 @@
         <v>0.0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0</v>
+        <v>2207.45</v>
       </c>
       <c r="BR3" t="n">
         <v>0.0</v>
@@ -1759,13 +1744,13 @@
         <v>0.0</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.0791538157E8</v>
+        <v>0.0</v>
       </c>
       <c r="BV3" t="n">
         <v>0.0</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.0</v>
+        <v>17781.0</v>
       </c>
       <c r="BY3" t="n">
         <v>0.0</v>
@@ -1774,42 +1759,54 @@
         <v>0.0</v>
       </c>
       <c r="CB3" t="n">
-        <v>1317.6</v>
+        <v>120.53</v>
       </c>
       <c r="CC3" t="n">
-        <v>1317.6</v>
+        <v>105.73</v>
       </c>
       <c r="CD3" t="n">
         <v>0.0</v>
       </c>
       <c r="CE3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>117</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>124</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>128</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>117</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>126</v>
+      </c>
+      <c r="DB3" t="s">
         <v>108</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>109</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>112</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>115</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>109</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B4" t="s">
         <v>105</v>
@@ -1817,15 +1814,66 @@
       <c r="C4" t="s">
         <v>106</v>
       </c>
-      <c r="N4" t="s">
+      <c r="E4" t="s">
         <v>107</v>
       </c>
+      <c r="G4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" t="s">
+        <v>108</v>
+      </c>
+      <c r="P4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>110</v>
+      </c>
+      <c r="W4" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>117</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>119</v>
+      </c>
       <c r="BK4" t="n">
         <v>0.0</v>
       </c>
       <c r="BL4" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN4" t="n">
+        <v>683.24</v>
+      </c>
       <c r="BO4" t="n">
         <v>0.0</v>
       </c>
@@ -1833,7 +1881,7 @@
         <v>0.0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0</v>
+        <v>2202.55</v>
       </c>
       <c r="BR4" t="n">
         <v>0.0</v>
@@ -1845,13 +1893,13 @@
         <v>0.0</v>
       </c>
       <c r="BU4" t="n">
-        <v>1432679.33</v>
+        <v>0.0</v>
       </c>
       <c r="BV4" t="n">
         <v>0.0</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.0</v>
+        <v>17781.0</v>
       </c>
       <c r="BY4" t="n">
         <v>0.0</v>
@@ -1860,37 +1908,49 @@
         <v>0.0</v>
       </c>
       <c r="CB4" t="n">
-        <v>17.5</v>
+        <v>121.07</v>
       </c>
       <c r="CC4" t="n">
-        <v>16.94</v>
+        <v>105.67</v>
       </c>
       <c r="CD4" t="n">
         <v>0.0</v>
       </c>
       <c r="CE4" t="s">
+        <v>120</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>117</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>121</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>122</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>123</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>124</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>106</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>130</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>117</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>126</v>
+      </c>
+      <c r="DB4" t="s">
         <v>108</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>109</v>
-      </c>
-      <c r="CG4" t="s">
-        <v>110</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>111</v>
-      </c>
-      <c r="CI4" t="s">
-        <v>112</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>117</v>
-      </c>
-      <c r="CQ4" t="s">
-        <v>109</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -1911,7 +1971,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1922,46 +1982,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -1992,10 +2019,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -2025,13 +2052,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -2065,10 +2092,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>61</v>
@@ -2080,7 +2107,7 @@
         <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -2101,14 +2128,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="90.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2118,11 +2142,9 @@
     <col min="17" max="17" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2143,64 +2165,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>77</v>
@@ -2215,467 +2237,52 @@
         <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F2" t="s">
-        <v>309</v>
-      </c>
-      <c r="G2" t="s">
-        <v>310</v>
-      </c>
-      <c r="H2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I2" t="s">
-        <v>276</v>
-      </c>
-      <c r="J2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K2" t="s">
-        <v>276</v>
-      </c>
-      <c r="L2" t="s">
-        <v>277</v>
-      </c>
-      <c r="M2" t="n">
-        <v>124.4</v>
-      </c>
-      <c r="P2" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>106</v>
-      </c>
-      <c r="R2" t="s">
-        <v>171</v>
-      </c>
-      <c r="S2" t="s">
-        <v>311</v>
-      </c>
-      <c r="T2" t="s">
-        <v>312</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1209.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.248167762E7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.248167762E7</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E3" t="s">
-        <v>313</v>
-      </c>
-      <c r="F3" t="s">
-        <v>276</v>
-      </c>
-      <c r="G3" t="s">
-        <v>314</v>
-      </c>
-      <c r="H3" t="s">
-        <v>276</v>
-      </c>
-      <c r="I3" t="s">
-        <v>276</v>
-      </c>
-      <c r="J3" t="s">
-        <v>276</v>
-      </c>
-      <c r="K3" t="s">
-        <v>276</v>
-      </c>
-      <c r="L3" t="s">
-        <v>277</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1119.65</v>
-      </c>
-      <c r="P3" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>106</v>
-      </c>
-      <c r="R3" t="s">
-        <v>169</v>
-      </c>
-      <c r="S3" t="s">
-        <v>315</v>
-      </c>
-      <c r="T3" t="s">
-        <v>316</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>14883.84</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>9.489235501E7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>9.489235501E7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>307</v>
-      </c>
-      <c r="E4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F4" t="s">
-        <v>276</v>
-      </c>
-      <c r="G4" t="s">
-        <v>317</v>
-      </c>
-      <c r="H4" t="s">
-        <v>276</v>
-      </c>
-      <c r="I4" t="s">
-        <v>276</v>
-      </c>
-      <c r="J4" t="s">
-        <v>276</v>
-      </c>
-      <c r="K4" t="s">
-        <v>276</v>
-      </c>
-      <c r="L4" t="s">
-        <v>277</v>
-      </c>
-      <c r="M4" t="n">
-        <v>125.17</v>
-      </c>
-      <c r="P4" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>106</v>
-      </c>
-      <c r="R4" t="s">
-        <v>193</v>
-      </c>
-      <c r="S4" t="s">
-        <v>318</v>
-      </c>
-      <c r="T4" t="s">
-        <v>319</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>3529.44</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.025178728E7</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.025178728E7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>307</v>
-      </c>
-      <c r="E5" t="s">
-        <v>320</v>
-      </c>
-      <c r="F5" t="s">
-        <v>276</v>
-      </c>
-      <c r="G5" t="s">
-        <v>321</v>
-      </c>
-      <c r="H5" t="s">
-        <v>276</v>
-      </c>
-      <c r="I5" t="s">
-        <v>276</v>
-      </c>
-      <c r="J5" t="s">
-        <v>276</v>
-      </c>
-      <c r="K5" t="s">
-        <v>276</v>
-      </c>
-      <c r="L5" t="s">
-        <v>277</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1192.43</v>
-      </c>
-      <c r="P5" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>106</v>
-      </c>
-      <c r="R5" t="s">
-        <v>191</v>
-      </c>
-      <c r="S5" t="s">
-        <v>322</v>
-      </c>
-      <c r="T5" t="s">
-        <v>323</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>7560.0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>9.766359429E7</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>9.766359429E7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E6" t="s">
-        <v>324</v>
-      </c>
-      <c r="F6" t="s">
-        <v>276</v>
-      </c>
-      <c r="G6" t="s">
-        <v>325</v>
-      </c>
-      <c r="H6" t="s">
-        <v>326</v>
-      </c>
-      <c r="I6" t="s">
-        <v>276</v>
-      </c>
-      <c r="J6" t="s">
-        <v>276</v>
-      </c>
-      <c r="K6" t="s">
-        <v>276</v>
-      </c>
-      <c r="L6" t="s">
-        <v>277</v>
-      </c>
-      <c r="M6" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="P6" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R6" t="s">
-        <v>201</v>
-      </c>
-      <c r="S6" t="s">
-        <v>327</v>
-      </c>
-      <c r="T6" t="s">
-        <v>328</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6789.84</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1432679.33</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1432679.33</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -2696,7 +2303,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2727,824 +2334,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F2" t="s">
-        <v>329</v>
-      </c>
-      <c r="G2" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2596633.77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M2" t="s">
-        <v>277</v>
-      </c>
-      <c r="N2" t="n">
-        <v>124.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" t="s">
-        <v>329</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1124083.88</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M3" t="s">
-        <v>277</v>
-      </c>
-      <c r="N3" t="n">
-        <v>124.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>307</v>
-      </c>
-      <c r="E4" t="s">
-        <v>126</v>
-      </c>
-      <c r="F4" t="s">
-        <v>329</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>590144.04</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M4" t="s">
-        <v>277</v>
-      </c>
-      <c r="N4" t="n">
-        <v>124.4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>307</v>
-      </c>
-      <c r="E5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7500.0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>8397375.0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M5" t="s">
-        <v>277</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1119.65</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E6" t="s">
-        <v>124</v>
-      </c>
-      <c r="F6" t="s">
-        <v>329</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I6" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.214473223E7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M6" t="s">
-        <v>277</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1119.65</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E7" t="s">
-        <v>126</v>
-      </c>
-      <c r="F7" t="s">
-        <v>329</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H7" t="s">
-        <v>122</v>
-      </c>
-      <c r="I7" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2760166.42</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M7" t="s">
-        <v>277</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1119.65</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>307</v>
-      </c>
-      <c r="E8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" t="s">
-        <v>329</v>
-      </c>
-      <c r="G8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H8" t="s">
-        <v>122</v>
-      </c>
-      <c r="I8" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7116926.63</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M8" t="s">
-        <v>277</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1119.65</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>307</v>
-      </c>
-      <c r="E9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" t="s">
-        <v>329</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I9" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>269109.42</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M9" t="s">
-        <v>277</v>
-      </c>
-      <c r="N9" t="n">
-        <v>125.17</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>307</v>
-      </c>
-      <c r="E10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" t="s">
-        <v>329</v>
-      </c>
-      <c r="G10" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I10" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1184081.43</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M10" t="s">
-        <v>277</v>
-      </c>
-      <c r="N10" t="n">
-        <v>125.17</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
-        <v>307</v>
-      </c>
-      <c r="E11" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" t="s">
-        <v>329</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I11" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>512589.36</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M11" t="s">
-        <v>277</v>
-      </c>
-      <c r="N11" t="n">
-        <v>125.17</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
-        <v>307</v>
-      </c>
-      <c r="E12" t="s">
-        <v>126</v>
-      </c>
-      <c r="F12" t="s">
-        <v>329</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H12" t="s">
-        <v>122</v>
-      </c>
-      <c r="I12" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2624709.1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M12" t="s">
-        <v>277</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1192.43</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="s">
-        <v>307</v>
-      </c>
-      <c r="E13" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" t="s">
-        <v>329</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I13" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>7324769.57</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M13" t="s">
-        <v>277</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1192.43</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="s">
-        <v>307</v>
-      </c>
-      <c r="E14" t="s">
-        <v>124</v>
-      </c>
-      <c r="F14" t="s">
-        <v>329</v>
-      </c>
-      <c r="G14" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H14" t="s">
-        <v>122</v>
-      </c>
-      <c r="I14" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.154872002E7</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M14" t="s">
-        <v>277</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1192.43</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="s">
-        <v>307</v>
-      </c>
-      <c r="E15" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" t="s">
-        <v>329</v>
-      </c>
-      <c r="G15" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="H15" t="s">
-        <v>122</v>
-      </c>
-      <c r="I15" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>214901.9</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M15" t="s">
-        <v>277</v>
-      </c>
-      <c r="N15" t="n">
-        <v>16.94</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>307</v>
-      </c>
-      <c r="E16" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16" t="s">
-        <v>329</v>
-      </c>
-      <c r="G16" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H16" t="s">
-        <v>122</v>
-      </c>
-      <c r="I16" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>227353.09</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M16" t="s">
-        <v>277</v>
-      </c>
-      <c r="N16" t="n">
-        <v>16.94</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>116</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>307</v>
-      </c>
-      <c r="E17" t="s">
-        <v>126</v>
-      </c>
-      <c r="F17" t="s">
-        <v>329</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H17" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>51671.16</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M17" t="s">
-        <v>277</v>
-      </c>
-      <c r="N17" t="n">
-        <v>16.94</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>116</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="s">
-        <v>307</v>
-      </c>
-      <c r="E18" t="s">
-        <v>125</v>
-      </c>
-      <c r="F18" t="s">
-        <v>107</v>
-      </c>
-      <c r="G18" t="n">
-        <v>24750.0</v>
-      </c>
-      <c r="H18" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>419265.0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M18" t="s">
-        <v>277</v>
-      </c>
-      <c r="N18" t="n">
-        <v>16.94</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3578,19 +2437,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +2470,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3623,170 +2482,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D2" t="n">
-        <v>8241010.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.4741366E7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" t="n">
-        <v>8397375.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3350310.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2893818.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.2732801E7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7837358.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D9" t="n">
-        <v>227353.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" t="n">
-        <v>51671.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D11" t="n">
-        <v>214901.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>116</v>
-      </c>
-      <c r="B12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" t="n">
-        <v>419265.0</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -3807,16 +2512,16 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3827,115 +2532,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>333</v>
+        <v>293</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>334</v>
+        <v>294</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>337</v>
+        <v>297</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4.56226E8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>340</v>
-      </c>
-      <c r="H2" t="s">
-        <v>341</v>
-      </c>
-      <c r="I2" t="s">
-        <v>182</v>
-      </c>
-      <c r="J2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E3" t="s">
-        <v>342</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.48762E8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>340</v>
-      </c>
-      <c r="H3" t="s">
-        <v>343</v>
-      </c>
-      <c r="I3" t="s">
-        <v>188</v>
-      </c>
-      <c r="J3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E4" t="s">
-        <v>344</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.07544E8</v>
-      </c>
-      <c r="G4" t="s">
-        <v>340</v>
-      </c>
-      <c r="H4" t="s">
-        <v>345</v>
-      </c>
-      <c r="I4" t="s">
-        <v>199</v>
-      </c>
-      <c r="J4" t="s">
-        <v>344</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -3956,7 +2574,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3964,13 +2583,55 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D3" t="s">
         <v>301</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>346</v>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D4" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -3996,7 +2657,7 @@
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="107.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="157.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -4013,49 +2674,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2">
@@ -4063,28 +2724,31 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="J2" t="s">
-        <v>147</v>
+        <v>155</v>
+      </c>
+      <c r="O2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="3">
@@ -4092,28 +2756,19 @@
         <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G3" t="s">
-        <v>151</v>
-      </c>
-      <c r="I3" t="s">
-        <v>146</v>
-      </c>
-      <c r="J3" t="s">
-        <v>147</v>
+        <v>158</v>
+      </c>
+      <c r="M3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="4">
@@ -4121,211 +2776,319 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="E4" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="F4" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="G4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" t="s">
-        <v>154</v>
-      </c>
-      <c r="K4" t="s">
-        <v>155</v>
-      </c>
-      <c r="L4" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="F5" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="G5" t="s">
-        <v>153</v>
-      </c>
-      <c r="H5" t="s">
-        <v>154</v>
-      </c>
-      <c r="K5" t="s">
-        <v>155</v>
-      </c>
-      <c r="L5" t="s">
-        <v>156</v>
+        <v>166</v>
+      </c>
+      <c r="M5" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="F6" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="G6" t="s">
-        <v>145</v>
-      </c>
-      <c r="I6" t="s">
-        <v>146</v>
+        <v>169</v>
+      </c>
+      <c r="H6" t="s">
+        <v>170</v>
       </c>
       <c r="J6" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I7" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="J7" t="s">
-        <v>147</v>
+        <v>155</v>
+      </c>
+      <c r="O7" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" t="s">
         <v>157</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>158</v>
       </c>
-      <c r="G8" t="s">
-        <v>159</v>
-      </c>
-      <c r="I8" t="s">
-        <v>146</v>
-      </c>
-      <c r="J8" t="s">
-        <v>147</v>
+      <c r="M8" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="F9" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="G9" t="s">
-        <v>151</v>
-      </c>
-      <c r="I9" t="s">
-        <v>146</v>
-      </c>
-      <c r="J9" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" t="s">
+        <v>165</v>
+      </c>
+      <c r="G10" t="s">
+        <v>166</v>
+      </c>
+      <c r="M10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F11" t="s">
+        <v>168</v>
+      </c>
+      <c r="G11" t="s">
+        <v>169</v>
+      </c>
+      <c r="H11" t="s">
+        <v>170</v>
+      </c>
+      <c r="J11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F12" t="s">
         <v>152</v>
       </c>
-      <c r="C10" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" t="s">
-        <v>149</v>
-      </c>
-      <c r="F10" t="s">
-        <v>150</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="G12" t="s">
         <v>153</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I12" t="s">
         <v>154</v>
       </c>
-      <c r="K10" t="s">
+      <c r="J12" t="s">
         <v>155</v>
       </c>
-      <c r="L10" t="s">
+      <c r="O12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" t="s">
         <v>156</v>
+      </c>
+      <c r="C13" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" t="s">
+        <v>157</v>
+      </c>
+      <c r="G13" t="s">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" t="s">
+        <v>163</v>
+      </c>
+      <c r="G14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" t="s">
+        <v>165</v>
+      </c>
+      <c r="G15" t="s">
+        <v>166</v>
+      </c>
+      <c r="M15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>167</v>
+      </c>
+      <c r="F16" t="s">
+        <v>168</v>
+      </c>
+      <c r="G16" t="s">
+        <v>169</v>
+      </c>
+      <c r="H16" t="s">
+        <v>170</v>
+      </c>
+      <c r="J16" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -4348,12 +3111,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>364</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>365</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -4385,55 +3148,55 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>366</v>
+        <v>321</v>
       </c>
       <c r="C1" t="s">
-        <v>367</v>
+        <v>322</v>
       </c>
       <c r="D1" t="s">
-        <v>368</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>369</v>
+        <v>324</v>
       </c>
       <c r="C2" t="s">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>369</v>
+        <v>324</v>
       </c>
       <c r="C3" t="s">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>369</v>
+        <v>324</v>
       </c>
       <c r="C4" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -4456,7 +3219,7 @@
   <cols>
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="72.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -4467,22 +3230,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
@@ -4490,16 +3253,16 @@
         <v>104</v>
       </c>
       <c r="B2" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3">
@@ -4507,16 +3270,16 @@
         <v>104</v>
       </c>
       <c r="B3" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
@@ -4524,16 +3287,16 @@
         <v>104</v>
       </c>
       <c r="B4" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="C4" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E4" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5">
@@ -4541,16 +3304,16 @@
         <v>104</v>
       </c>
       <c r="B5" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="C5" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="D5" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E5" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6">
@@ -4558,24 +3321,24 @@
         <v>104</v>
       </c>
       <c r="B6" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="E6" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="B7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="C7" t="s">
         <v>176</v>
@@ -4589,64 +3352,64 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="B8" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="C8" t="s">
         <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E8" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="B9" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C9" t="s">
         <v>181</v>
       </c>
       <c r="D9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B10" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="C10" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" t="s">
         <v>183</v>
-      </c>
-      <c r="E10" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B11" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
         <v>184</v>
@@ -4657,206 +3420,87 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B12" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B13" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="C13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E13" t="s">
-        <v>187</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B14" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="C14" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E14" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B15" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C15" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="D15" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E15" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B16" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E16" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="C17" t="s">
-        <v>168</v>
-      </c>
-      <c r="D17" t="s">
-        <v>193</v>
-      </c>
-      <c r="E17" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>116</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="C18" t="s">
-        <v>173</v>
-      </c>
-      <c r="D18" t="s">
-        <v>195</v>
-      </c>
-      <c r="E18" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="C19" t="s">
-        <v>176</v>
-      </c>
-      <c r="D19" t="s">
-        <v>197</v>
-      </c>
-      <c r="E19" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B20" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C20" t="s">
-        <v>179</v>
-      </c>
-      <c r="D20" t="s">
-        <v>198</v>
-      </c>
-      <c r="E20" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B21" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C21" t="s">
-        <v>181</v>
-      </c>
-      <c r="D21" t="s">
-        <v>199</v>
-      </c>
-      <c r="E21" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>116</v>
-      </c>
-      <c r="B22" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="C22" t="s">
-        <v>164</v>
-      </c>
-      <c r="D22" t="s">
-        <v>200</v>
-      </c>
-      <c r="E22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="C23" t="s">
-        <v>168</v>
-      </c>
-      <c r="D23" t="s">
-        <v>201</v>
-      </c>
-      <c r="E23" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -4879,7 +3523,7 @@
   <cols>
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -4892,28 +3536,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2">
@@ -4924,29 +3568,56 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>152</v>
+        <v>108</v>
+      </c>
+      <c r="D2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>108</v>
+      </c>
+      <c r="D3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>108</v>
+      </c>
+      <c r="D4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -4970,6 +3641,7 @@
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -4978,19 +3650,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2">
@@ -5001,38 +3673,47 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D2" t="n">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -5066,22 +3747,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -5123,61 +3804,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>302</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>348</v>
+        <v>303</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>350</v>
+        <v>305</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>351</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>352</v>
+        <v>307</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>354</v>
+        <v>309</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>355</v>
+        <v>310</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>356</v>
+        <v>311</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>357</v>
+        <v>312</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>60</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>358</v>
+        <v>313</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>359</v>
+        <v>314</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>362</v>
+        <v>317</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>363</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -5201,8 +3882,9 @@
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="106.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="131.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -5217,8 +3899,7 @@
     <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="34" max="34" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -5265,58 +3946,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>77</v>
@@ -5328,19 +4009,19 @@
         <v>78</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>71</v>
@@ -5355,25 +4036,25 @@
         <v>64</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>61</v>
@@ -5382,94 +4063,94 @@
         <v>74</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AV1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="BH1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
@@ -5480,52 +4161,52 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D2" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F2" t="s">
-        <v>276</v>
+        <v>203</v>
       </c>
       <c r="G2" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="H2" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="I2" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="J2" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="K2" t="n">
-        <v>1244.05</v>
+        <v>2631.0</v>
       </c>
       <c r="L2" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="M2" t="n">
-        <v>48.0</v>
+        <v>46.0</v>
       </c>
       <c r="T2" t="n">
-        <v>1244.05</v>
+        <v>308.72</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.1737403264E8</v>
+        <v>0.0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.1737403264E8</v>
+        <v>0.0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.0</v>
+        <v>17781.0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0</v>
+        <v>6445.95</v>
       </c>
       <c r="AF2" t="n">
         <v>0.0</v>
@@ -5539,6 +4220,9 @@
       <c r="AI2" t="n">
         <v>0.0</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>2.45</v>
+      </c>
       <c r="AK2" t="n">
         <v>0.0</v>
       </c>
@@ -5548,73 +4232,76 @@
       <c r="AN2" t="n">
         <v>0.0</v>
       </c>
-      <c r="AR2" t="s">
-        <v>152</v>
+      <c r="AS2" t="s">
+        <v>266</v>
       </c>
       <c r="AY2" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.0</v>
       </c>
+      <c r="BO2" t="s">
+        <v>108</v>
+      </c>
       <c r="BR2" t="s">
-        <v>279</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="D3" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="E3" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="F3" t="s">
-        <v>276</v>
+        <v>203</v>
       </c>
       <c r="G3" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="H3" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="I3" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="J3" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="K3" t="n">
-        <v>1317.6</v>
+        <v>901.0</v>
       </c>
       <c r="L3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="M3" t="n">
-        <v>48.0</v>
+        <v>19.0</v>
       </c>
       <c r="T3" t="n">
-        <v>1317.6</v>
+        <v>105.73</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.0791538157E8</v>
+        <v>0.0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.0791538157E8</v>
+        <v>0.0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.0</v>
+        <v>17781.0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0</v>
+        <v>2207.45</v>
       </c>
       <c r="AF3" t="n">
         <v>0.0</v>
@@ -5628,6 +4315,9 @@
       <c r="AI3" t="n">
         <v>0.0</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>2.45</v>
+      </c>
       <c r="AK3" t="n">
         <v>0.0</v>
       </c>
@@ -5637,73 +4327,76 @@
       <c r="AN3" t="n">
         <v>0.0</v>
       </c>
-      <c r="AR3" t="s">
-        <v>152</v>
+      <c r="AS3" t="s">
+        <v>266</v>
       </c>
       <c r="AY3" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="BJ3" t="n">
         <v>0.0</v>
       </c>
+      <c r="BO3" t="s">
+        <v>108</v>
+      </c>
       <c r="BR3" t="s">
-        <v>279</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="E4" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="F4" t="s">
-        <v>276</v>
+        <v>203</v>
       </c>
       <c r="G4" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="H4" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="I4" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="J4" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="K4" t="n">
-        <v>242.0</v>
+        <v>899.0</v>
       </c>
       <c r="L4" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="M4" t="n">
-        <v>11.0</v>
+        <v>20.0</v>
       </c>
       <c r="T4" t="n">
-        <v>16.94</v>
+        <v>105.67</v>
       </c>
       <c r="Z4" t="n">
-        <v>1432679.33</v>
+        <v>0.0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1432679.33</v>
+        <v>0.0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.0</v>
+        <v>17781.0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0</v>
+        <v>2202.55</v>
       </c>
       <c r="AF4" t="n">
         <v>0.0</v>
@@ -5717,6 +4410,9 @@
       <c r="AI4" t="n">
         <v>0.0</v>
       </c>
+      <c r="AJ4" t="n">
+        <v>2.45</v>
+      </c>
       <c r="AK4" t="n">
         <v>0.0</v>
       </c>
@@ -5726,17 +4422,20 @@
       <c r="AN4" t="n">
         <v>0.0</v>
       </c>
-      <c r="AR4" t="s">
-        <v>152</v>
+      <c r="AS4" t="s">
+        <v>266</v>
       </c>
       <c r="AY4" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="BJ4" t="n">
         <v>0.0</v>
       </c>
+      <c r="BO4" t="s">
+        <v>108</v>
+      </c>
       <c r="BR4" t="s">
-        <v>279</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -5782,58 +4481,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
